--- a/output/第10期計画_中間報告会議議事録の校正結果.xlsx
+++ b/output/第10期計画_中間報告会議議事録の校正結果.xlsx
@@ -570,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -591,7 +591,7 @@
     <row r="2" ht="56" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>受領版を点検し、13件を校正しました。あわせてご確認をお願いする事項が5件、8月工程に照らした網羅性の点検で記載のない事項が7件あります。</t>
+          <t>受領版を点検し、15件を校正しました。あわせてご確認をお願いする事項が5件、8月工程に照らした網羅性の点検で記載のない事項が7件あります。</t>
         </is>
       </c>
     </row>
@@ -916,97 +916,93 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
+    <row r="17" ht="48" customHeight="1">
+      <c r="A17" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>記載の追加</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>2件</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>打合せでご確認をお願いした3点のうち、①第9期計画の評価・検証 中間報告と②施策体系新旧対照表の記載がありませんでした。令和8年8月28日の発注者のご指示により、本文の2箇所に加えました。あわせて期限を明記しました。</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="n"/>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>校正済</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>【2　とくにご確認をお願いしたい3件】</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="32" customHeight="1">
-      <c r="A19" s="4" t="inlineStr">
+    <row r="20" ht="32" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>事項</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>受領版</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>校正後</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>理由</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>重要度</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="68" customHeight="1">
-      <c r="A20" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>業務期間</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>令和8年3月26日</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>令和9年3月26日まで</t>
-        </is>
-      </c>
-      <c r="E20" s="6" t="inlineStr">
-        <is>
-          <t>令和8年3月26日は本業務の着手前の日付です。3町へ展開される文書であり、工程の前提が誤って伝わります。</t>
-        </is>
-      </c>
-      <c r="F20" s="8" t="inlineStr">
-        <is>
-          <t>高</t>
         </is>
       </c>
     </row>
     <row r="21" ht="68" customHeight="1">
       <c r="A21" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>代表KPIの判定</t>
+          <t>業務期間</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>④は達成済み</t>
+          <t>令和8年3月26日</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>④は現時点で達成（中間判定）</t>
+          <t>令和9年3月26日まで</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>契約期間が令和9年3月26日までで、第9期最終年度末（令和9年3月31日）より前に終了します。中間報告の判定はいずれも中間判定であり、「達成済み」は最終評価が確定したように読まれます。</t>
+          <t>令和8年3月26日は本業務の着手前の日付です。3町へ展開される文書であり、工程の前提が誤って伝わります。</t>
         </is>
       </c>
       <c r="F21" s="8" t="inlineStr">
@@ -1017,36 +1013,66 @@
     </row>
     <row r="22" ht="68" customHeight="1">
       <c r="A22" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>代表KPIの判定</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>④は達成済み</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>④は現時点で達成（中間判定）</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>契約期間が令和9年3月26日までで、第9期最終年度末（令和9年3月31日）より前に終了します。中間報告の判定はいずれも中間判定であり、「達成済み」は最終評価が確定したように読まれます。</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="68" customHeight="1">
+      <c r="A23" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>文書プロパティ</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>題名に「小野町」「RED TEAM」、作成者に個人名等</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="D23" s="6" t="inlineStr">
         <is>
           <t>題名・作成者を本件の内容に置き換え</t>
         </is>
       </c>
-      <c r="E22" s="6" t="inlineStr">
+      <c r="E23" s="6" t="inlineStr">
         <is>
           <t>本文には現れないため通読では気づきません。構成3町へ展開される文書であり、送付前の是正が必要です。</t>
         </is>
       </c>
-      <c r="F22" s="8" t="inlineStr">
+      <c r="F23" s="8" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="96" customHeight="1">
-      <c r="A24" s="10" t="inlineStr">
+    <row r="25" ht="96" customHeight="1">
+      <c r="A25" s="10" t="inlineStr">
         <is>
           <t>注1）本文の書式を保つため、受領版のcontent.xmlの文字列置換により校正しました。段落・表・書式は受領版のままです。
 注2）校正を反映した議事録は「第10期計画_中間報告会議議事録_令和8年8月26日.odt」です。
@@ -1056,21 +1082,22 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="17">
     <mergeCell ref="D8:E8"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="D6:E6"/>
     <mergeCell ref="D16:E16"/>
-    <mergeCell ref="A24:F24"/>
     <mergeCell ref="D7:E7"/>
     <mergeCell ref="D10:E10"/>
+    <mergeCell ref="A19:F19"/>
     <mergeCell ref="D15:E15"/>
     <mergeCell ref="D11:E11"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="D13:E13"/>
+    <mergeCell ref="D17:E17"/>
     <mergeCell ref="D14:E14"/>
-    <mergeCell ref="A18:F18"/>
     <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A25:F25"/>
     <mergeCell ref="D9:E9"/>
     <mergeCell ref="D12:E12"/>
   </mergeCells>
@@ -1084,7 +1111,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1098,7 +1125,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>校正の一覧（13件）</t>
+          <t>校正の一覧（15件）</t>
         </is>
       </c>
     </row>
@@ -1503,46 +1530,106 @@
     </row>
     <row r="17" ht="76" customHeight="1">
       <c r="A17" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>記載の追加</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>評価の枠組み</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>ご提示した計画骨子をご確認いただく（来週水曜日までにご確認いただくことを確認）。</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>ご提示した①第9期計画の評価・検証 中間報告、②施策体系新旧対照表、③計画骨子案の3点をご確認いただく（来週水曜日までにご確認いただくことを確認）。</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>打合せでは①中間報告、②施策体系新旧対照表、③計画骨子案の3点についてご確認をいただくこととなりました（確認事項No.39）。議事録は③のみの記載でした。令和8年8月28日に発注者のご指示により①②を加えました。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="76" customHeight="1">
+      <c r="A18" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>記載の追加</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>連携事項（大雪地区広域連合 事務局 様）</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>・本日ご教示した計画骨子をご確認いただく。</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>・本日ご提示した①第9期計画の評価・検証 中間報告、②施策体系新旧対照表、③計画骨子案の3点をご確認いただく（令和8年9月2日（水）まで）。</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>同上。あわせて、打合せで設定した期限（令和8年9月2日（水））を連携事項に明記します。「ご教示」は受託者から発注者への説明を指す語として適切でないため、「ご提示」に改めます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="76" customHeight="1">
+      <c r="A19" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B19" s="11" t="inlineStr">
         <is>
           <t>文書プロパティ</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C19" s="6" t="inlineStr">
         <is>
           <t>meta.xml</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D19" s="6" t="inlineStr">
         <is>
           <t>題名「小野町 第10期計画策定業務 キックオフ会議議事録（RED TEAM・MECE整理版）」、作成者「OpenAI」「熊谷 麻由」、説明「generated by python-docx」</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E19" s="6" t="inlineStr">
         <is>
           <t>題名「大雪地区広域連合 第10期介護保険事業計画 第9期計画の評価・検証 中間報告 会議議事録（令和8年8月26日開催）」、作成者「ビズアップ公共コンサルティング株式会社」</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="F19" s="6" t="inlineStr">
         <is>
           <t>本文には現れませんが、ファイルのプロパティに他自治体名（小野町）、内部用語（RED TEAM）、作成支援に用いた道具の名称、個人名が残っています。構成3町へ展開される文書であり、送付前の是正が必要です。</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="56" customHeight="1">
-      <c r="A19" s="10" t="inlineStr">
-        <is>
-          <t>注1）本文を置換した箇所は次のとおりです。No.1 1箇所、No.2 1箇所、No.3 1箇所、No.4 1箇所、No.5 1箇所、No.6 1箇所、No.7 1箇所、No.8 2箇所、No.9 1箇所、No.10 1箇所、No.11 1箇所、No.12 1箇所。No.8は、No.4で「大雪広域連合様おいて」を先に置換したため、残る2箇所が対象となっています。
+    <row r="21" ht="56" customHeight="1">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>注1）本文を置換した箇所は次のとおりです。No.1 1箇所、No.2 1箇所、No.3 1箇所、No.4 1箇所、No.5 1箇所、No.6 1箇所、No.7 1箇所、No.8 2箇所、No.9 1箇所、No.10 1箇所、No.11 1箇所、No.12 1箇所、No.14 1箇所、No.15 1箇所。No.8は、No.4で「大雪広域連合様おいて」を先に置換したため、残る2箇所が対象となっています。
 注2）No.13（文書プロパティ）は本文の置換ではなく、meta.xmlの書き換えによります。</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A19:F19"/>
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A21:F21"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1648,12 +1735,12 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>確認をお願いした3点の記載</t>
+          <t>確認をお願いした3点の記載【反映済】</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>議事録では「ご提示した計画骨子をご確認いただく」とされていますが、打合せでは①中間報告、②施策体系新旧対照表、③計画骨子案の3点についてご確認をいただくこととなりました（確認事項No.39）。議事録に①②を加えてよいかご確認ください。</t>
+          <t>議事録は「ご提示した計画骨子をご確認いただく」と③のみの記載でした。打合せでは①第9期計画の評価・検証 中間報告、②施策体系新旧対照表、③計画骨子案の3点についてご確認をいただくこととなりました（確認事項No.39）。令和8年8月28日に発注者より①②を加えるようご指示をいただき、本文の2箇所（評価の枠組み・連携事項）に反映しました（校正No.14・15）。あわせて連携事項に期限（令和8年9月2日（水））を明記しました。</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">

--- a/output/第10期計画_中間報告会議議事録の校正結果.xlsx
+++ b/output/第10期計画_中間報告会議議事録の校正結果.xlsx
@@ -570,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -591,7 +591,7 @@
     <row r="2" ht="56" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>受領版を点検し、15件を校正しました。あわせてご確認をお願いする事項が5件、8月工程に照らした網羅性の点検で記載のない事項が7件あります。</t>
+          <t>受領版を点検し、17件を校正しました。あわせてご確認をお願いする事項が5件、8月工程に照らした網羅性の点検で記載のない事項が7件あります。</t>
         </is>
       </c>
     </row>
@@ -927,12 +927,12 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>2件</t>
+          <t>3件</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>打合せでご確認をお願いした3点のうち、①第9期計画の評価・検証 中間報告と②施策体系新旧対照表の記載がありませんでした。令和8年8月28日の発注者のご指示により、本文の2箇所に加えました。あわせて期限を明記しました。</t>
+          <t>①打合せでご確認をお願いした3点のうち第9期計画の評価・検証 中間報告と施策体系新旧対照表の記載がありませんでした（本文2箇所に追加、期限も明記）。②会議の目的に掲げた業務進捗の報告が本文にありませんでした（「業務進捗」の行を追加）。いずれも令和8年8月28日の発注者のご指示によります。</t>
         </is>
       </c>
       <c r="E17" s="7" t="n"/>
@@ -942,97 +942,93 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
+    <row r="18" ht="48" customHeight="1">
+      <c r="A18" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>事実の明確化</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>1件</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>年報・月報の「令和8年8月27日 受領」は大雪地区広域連合における受領であり、受託者はまだ受領していません。その旨を明記しました。</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="n"/>
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t>校正済</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>【2　とくにご確認をお願いしたい3件】</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="32" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
+    <row r="21" ht="32" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>事項</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>受領版</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>校正後</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>理由</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="F21" s="4" t="inlineStr">
         <is>
           <t>重要度</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="68" customHeight="1">
-      <c r="A21" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>業務期間</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>令和8年3月26日</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>令和9年3月26日まで</t>
-        </is>
-      </c>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>令和8年3月26日は本業務の着手前の日付です。3町へ展開される文書であり、工程の前提が誤って伝わります。</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="inlineStr">
-        <is>
-          <t>高</t>
         </is>
       </c>
     </row>
     <row r="22" ht="68" customHeight="1">
       <c r="A22" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>代表KPIの判定</t>
+          <t>業務期間</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>④は達成済み</t>
+          <t>令和8年3月26日</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>④は現時点で達成（中間判定）</t>
+          <t>令和9年3月26日まで</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>契約期間が令和9年3月26日までで、第9期最終年度末（令和9年3月31日）より前に終了します。中間報告の判定はいずれも中間判定であり、「達成済み」は最終評価が確定したように読まれます。</t>
+          <t>令和8年3月26日は本業務の着手前の日付です。3町へ展開される文書であり、工程の前提が誤って伝わります。</t>
         </is>
       </c>
       <c r="F22" s="8" t="inlineStr">
@@ -1043,36 +1039,66 @@
     </row>
     <row r="23" ht="68" customHeight="1">
       <c r="A23" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>代表KPIの判定</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>④は達成済み</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>④は現時点で達成（中間判定）</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>契約期間が令和9年3月26日までで、第9期最終年度末（令和9年3月31日）より前に終了します。中間報告の判定はいずれも中間判定であり、「達成済み」は最終評価が確定したように読まれます。</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="68" customHeight="1">
+      <c r="A24" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>文書プロパティ</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
         <is>
           <t>題名に「小野町」「RED TEAM」、作成者に個人名等</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D24" s="6" t="inlineStr">
         <is>
           <t>題名・作成者を本件の内容に置き換え</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="E24" s="6" t="inlineStr">
         <is>
           <t>本文には現れないため通読では気づきません。構成3町へ展開される文書であり、送付前の是正が必要です。</t>
         </is>
       </c>
-      <c r="F23" s="8" t="inlineStr">
+      <c r="F24" s="8" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="96" customHeight="1">
-      <c r="A25" s="10" t="inlineStr">
+    <row r="26" ht="96" customHeight="1">
+      <c r="A26" s="10" t="inlineStr">
         <is>
           <t>注1）本文の書式を保つため、受領版のcontent.xmlの文字列置換により校正しました。段落・表・書式は受領版のままです。
 注2）校正を反映した議事録は「第10期計画_中間報告会議議事録_令和8年8月26日.odt」です。
@@ -1082,22 +1108,23 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="18">
     <mergeCell ref="D8:E8"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="D6:E6"/>
     <mergeCell ref="D16:E16"/>
     <mergeCell ref="D7:E7"/>
     <mergeCell ref="D10:E10"/>
-    <mergeCell ref="A19:F19"/>
     <mergeCell ref="D15:E15"/>
     <mergeCell ref="D11:E11"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="D13:E13"/>
     <mergeCell ref="D17:E17"/>
+    <mergeCell ref="A26:F26"/>
     <mergeCell ref="D14:E14"/>
     <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A25:F25"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="A20:F20"/>
     <mergeCell ref="D9:E9"/>
     <mergeCell ref="D12:E12"/>
   </mergeCells>
@@ -1111,7 +1138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1125,7 +1152,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>校正の一覧（15件）</t>
+          <t>校正の一覧（17件）</t>
         </is>
       </c>
     </row>
@@ -1590,38 +1617,98 @@
     </row>
     <row r="19" ht="76" customHeight="1">
       <c r="A19" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>事実の明確化</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>必要書類の確認</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>…ご提供いただくことを確認（令和8年8月27日 受領）。</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>…ご提供いただくことを確認（令和8年8月27日に大雪地区広域連合において受領。受託者へは後日ご送付いただく）。</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>令和8年8月27日の受領は大雪地区広域連合における受領であり、受託者はまだ受領していません。そのままでは受託者が受領済みと読まれます（令和8年8月28日の発注者のご回答による）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="76" customHeight="1">
+      <c r="A20" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>記載の追加</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>2. 合意・確認された内容（行の追加）</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>（記載なし）</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>業務進捗　仕様書４(1)〜(12)の区分ごとに進捗を報告し、令和8年8月26日時点の全体の進捗が60％であることを確認。…</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>「1. 会議の目的と範囲」に「現時点における弊社の業務進捗を報告する」と掲げていますが、「2. 合意・確認された内容」に進捗の記載がありませんでした。令和8年8月28日の発注者のご指示により、行を1つ加えました。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="76" customHeight="1">
+      <c r="A21" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t>文書プロパティ</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
         <is>
           <t>meta.xml</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D21" s="6" t="inlineStr">
         <is>
           <t>題名「小野町 第10期計画策定業務 キックオフ会議議事録（RED TEAM・MECE整理版）」、作成者「OpenAI」「熊谷 麻由」、説明「generated by python-docx」</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="E21" s="6" t="inlineStr">
         <is>
           <t>題名「大雪地区広域連合 第10期介護保険事業計画 第9期計画の評価・検証 中間報告 会議議事録（令和8年8月26日開催）」、作成者「ビズアップ公共コンサルティング株式会社」</t>
         </is>
       </c>
-      <c r="F19" s="6" t="inlineStr">
+      <c r="F21" s="6" t="inlineStr">
         <is>
           <t>本文には現れませんが、ファイルのプロパティに他自治体名（小野町）、内部用語（RED TEAM）、作成支援に用いた道具の名称、個人名が残っています。構成3町へ展開される文書であり、送付前の是正が必要です。</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="56" customHeight="1">
-      <c r="A21" s="10" t="inlineStr">
-        <is>
-          <t>注1）本文を置換した箇所は次のとおりです。No.1 1箇所、No.2 1箇所、No.3 1箇所、No.4 1箇所、No.5 1箇所、No.6 1箇所、No.7 1箇所、No.8 2箇所、No.9 1箇所、No.10 1箇所、No.11 1箇所、No.12 1箇所、No.14 1箇所、No.15 1箇所。No.8は、No.4で「大雪広域連合様おいて」を先に置換したため、残る2箇所が対象となっています。
+    <row r="23" ht="56" customHeight="1">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>注1）本文を置換した箇所は次のとおりです。No.1 1箇所、No.2 1箇所、No.3 1箇所、No.4 1箇所、No.5 1箇所、No.6 1箇所、No.7 1箇所、No.8 2箇所、No.9 1箇所、No.10 1箇所、No.11 1箇所、No.12 1箇所、No.14 1箇所、No.15 1箇所、No.16 1箇所。No.8は、No.4で「大雪広域連合様おいて」を先に置換したため、残る2箇所が対象となっています。
 注2）No.13（文書プロパティ）は本文の置換ではなく、meta.xmlの書き換えによります。</t>
         </is>
       </c>
@@ -1629,8 +1716,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A21:F21"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A23:F23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1693,12 +1780,12 @@
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>開催日</t>
+          <t>開催日【回答済】</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>議事録は「令和8年8月26日（水）」です。受託者の記録（業務工程管理表 確認事項No.39・41、進捗の基準日）は令和8年8月25日としています。曜日は8月26日が水曜日であり議事録と整合しますが、8月25日は火曜日です。どちらが正しいかご教示ください。受託者の記録を議事録に合わせて改めます。</t>
+          <t>議事録の「令和8年8月26日（水）」が正しいとのご回答をいただきました（令和8年8月28日）。受託者の記録は令和8年8月25日としていたため、業務工程管理表の確認事項一覧、業務進捗報告書の状況基準日、従業員数の重複計上の整理、給付実績データの受領点検ほか9つのファイルを令和8年8月26日に改めました。</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
@@ -1714,12 +1801,12 @@
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>年報・月報の受領日</t>
+          <t>年報・月報の受領日【回答済】</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>「（令和8年8月27日 受領）」とありますが、受託者が令和8年8月28日に受領した9件（交付金評価3か年、要介護認定の状況、医療機関リスト等）に年報・月報は含まれていません。資料No.21（年報）・No.22（月報）は受託者の記録では未受領です。別便でのご送付があったか、ご確認をお願いします。</t>
+          <t>令和8年8月27日の受領は大雪地区広域連合におけるものであり、受託者へは後日ご送付いただくとのご回答をいただきました（令和8年8月28日）。議事録の記載を「令和8年8月27日に大雪地区広域連合において受領。受託者へは後日ご送付いただく」に改めました（校正No.16）。資料No.21（年報）・No.22（月報）は引き続き未受領として管理し、到着後に受領済みとします。</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -1755,12 +1842,12 @@
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>会議の目的と本文の対応</t>
+          <t>会議の目的と本文の対応【反映済】</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>「1. 会議の目的と範囲」に「現時点における弊社の業務進捗を報告する」とありますが、「2. 合意・確認された内容」に進捗の報告が記載されていません。業務進捗報告書（令和8年8月分・仕様書４(1)〜(12)の区分別、全体60％）の内容を1行加えることを提案します。</t>
+          <t>「1. 会議の目的と範囲」に「現時点における弊社の業務進捗を報告する」と掲げていましたが、「2. 合意・確認された内容」に進捗の報告がありませんでした。令和8年8月28日の発注者のご指示により、「業務進捗」の行を加えました（校正No.17）。仕様書４(1)〜(12)の区分別の進捗と全体60％を記載しています。</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
@@ -1775,12 +1862,12 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>出席者</t>
+          <t>出席者【回答済】</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>令和8年8月6日のキックオフ会議は「若山（課長）・村田・林・熊谷」の4名でした。本会議は「若山（課長）・林・熊谷」の3名の記載です。村田のご欠席で相違ないかご確認ください。</t>
+          <t>村田の欠席で相違ないとのご回答をいただきました（令和8年8月28日）。議事録の出席者欄は「若山（課長）・林・熊谷」の3名のままとします。</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
@@ -1789,12 +1876,13 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="76" customHeight="1">
+    <row r="11" ht="88" customHeight="1">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>注1）No.1（開催日）は、受託者の記録が令和8年8月25日、議事録が令和8年8月26日（水）です。令和8年8月26日は水曜日、8月25日は火曜日です。曜日は議事録と整合しています。
-注2）No.2（年報・月報の受領日）は、資料の受領の記録に関わるため、確定が必要です。
-注3）ご回答により、業務工程管理表の確認事項一覧及び必要事項の一覧を更新します。</t>
+          <t>注1）5件とも令和8年8月28日にご回答をいただき、対応を終えています。本シートは、ご回答の内容と、それに基づく反映の記録として残すものです。
+注2）No.1（開催日）は、令和8年8月26日（水）が正しいとのご回答により、受託者の記録9ファイル（業務工程管理表、業務進捗報告書、従業員数の重複計上の整理、給付実績データの受領点検、令和8年8月28日受領資料の点検結果、中間報告、必要事項の一覧、成果品の索引、進捗の一元管理）を令和8年8月26日に改めました。
+注3）No.2（年報・月報）は受託者への到着後に受領済みとします。それまでは必要事項の一覧の資料No.21・22を未受領のままとします。
+注4）本件は業務工程管理表の確認事項No.49に記録しています。</t>
         </is>
       </c>
     </row>
@@ -1949,19 +2037,19 @@
           <t>業務進捗の報告</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>記載なし</t>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>記載あり</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>会議の目的に掲げているが、本文に記載がない。仕様書４(1)〜(12)の区分別の進捗（全体60％）を報告している。</t>
+          <t>当初は会議の目的に掲げながら本文に記載がなかった。令和8年8月28日の発注者のご指示により、「業務進捗」の行を加えた（校正No.17）。</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>「2. 合意・確認された内容」に進捗の行を加えることを提案します。</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -2249,7 +2337,7 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>6件</t>
+          <t>7件</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -2268,7 +2356,7 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>8件</t>
+          <t>7件</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
